--- a/newsletter.xlsx
+++ b/newsletter.xlsx
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E109"/>
+  <dimension ref="A1:E110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1546,95 +1546,95 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
+          <t>10:00～12:30</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>懐かしい盆踊りの会</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>懐かしい盆踊りのボランティア会の打ち合わせ・練習</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>イ</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="n"/>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
           <t>14:00～16:30</t>
         </is>
       </c>
-      <c r="C46" s="7" t="inlineStr">
+      <c r="C47" s="7" t="inlineStr">
         <is>
           <t>NPO法人でんでん虫の会</t>
         </is>
       </c>
-      <c r="D46" s="7" t="inlineStr">
+      <c r="D47" s="7" t="inlineStr">
         <is>
           <t>おしゃべり会</t>
         </is>
       </c>
-      <c r="E46" s="8" t="inlineStr">
-        <is>
-          <t>イ</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="9" t="n"/>
-      <c r="B47" s="6" t="inlineStr">
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>イ</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="n"/>
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>10:00～12:20</t>
         </is>
       </c>
-      <c r="C47" s="7" t="inlineStr">
+      <c r="C48" s="7" t="inlineStr">
         <is>
           <t>からだケア</t>
         </is>
       </c>
-      <c r="D47" s="7" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
         <is>
           <t>からだケア</t>
         </is>
       </c>
-      <c r="E47" s="8" t="inlineStr">
-        <is>
-          <t>会</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>会</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>10月29日（木）</t>
         </is>
       </c>
-      <c r="B48" s="6" t="inlineStr">
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>18:30～20:30</t>
         </is>
       </c>
-      <c r="C48" s="7" t="inlineStr">
+      <c r="C49" s="7" t="inlineStr">
         <is>
           <t>一般社団法人アイ・オー・イー（IOE）</t>
         </is>
       </c>
-      <c r="D48" s="7" t="inlineStr">
+      <c r="D49" s="7" t="inlineStr">
         <is>
           <t>くまもとNPOカレッジ2026</t>
         </is>
       </c>
-      <c r="E48" s="8" t="inlineStr">
-        <is>
-          <t>イ</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="10" t="n"/>
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>10:00～12:00</t>
-        </is>
-      </c>
-      <c r="C49" s="7" t="inlineStr">
-        <is>
-          <t>特定非営利活動法人　教育支援プロジェクト・マスターズ熊本</t>
-        </is>
-      </c>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>トークの会</t>
-        </is>
-      </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>会</t>
+          <t>イ</t>
         </is>
       </c>
     </row>
@@ -1642,163 +1642,163 @@
       <c r="A50" s="10" t="n"/>
       <c r="B50" s="6" t="inlineStr">
         <is>
+          <t>10:00～12:00</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>特定非営利活動法人　教育支援プロジェクト・マスターズ熊本</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>トークの会</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>会</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="n"/>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
           <t>13:10～15:20</t>
         </is>
       </c>
-      <c r="C50" s="7" t="inlineStr">
+      <c r="C51" s="7" t="inlineStr">
         <is>
           <t>熊本「新老人の会」</t>
         </is>
       </c>
-      <c r="D50" s="7" t="inlineStr">
+      <c r="D51" s="7" t="inlineStr">
         <is>
           <t>スポーツ吹矢</t>
         </is>
       </c>
-      <c r="E50" s="8" t="inlineStr">
-        <is>
-          <t>会</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="9" t="n"/>
-      <c r="B51" s="6" t="inlineStr">
+      <c r="E51" s="8" t="inlineStr">
+        <is>
+          <t>会</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="n"/>
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>18:30～20:30</t>
         </is>
       </c>
-      <c r="C51" s="7" t="inlineStr">
+      <c r="C52" s="7" t="inlineStr">
         <is>
           <t>熊本フォークダンスクラブ</t>
         </is>
       </c>
-      <c r="D51" s="7" t="inlineStr">
+      <c r="D52" s="7" t="inlineStr">
         <is>
           <t>フォークダンス練習会</t>
         </is>
       </c>
-      <c r="E51" s="8" t="inlineStr">
-        <is>
-          <t>会</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>会</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>10月30日（金）</t>
         </is>
       </c>
-      <c r="B52" s="6" t="inlineStr">
+      <c r="B53" s="6" t="inlineStr">
         <is>
           <t>13:00～17:30</t>
         </is>
       </c>
-      <c r="C52" s="7" t="inlineStr">
+      <c r="C53" s="7" t="inlineStr">
         <is>
           <t>囲碁普及会</t>
         </is>
       </c>
-      <c r="D52" s="7" t="inlineStr">
+      <c r="D53" s="7" t="inlineStr">
         <is>
           <t>囲碁の研究と対局</t>
         </is>
       </c>
-      <c r="E52" s="8" t="inlineStr">
-        <is>
-          <t>イ</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="10" t="n"/>
-      <c r="B53" s="6" t="inlineStr">
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>イ</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="n"/>
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>9:30～12:30</t>
         </is>
       </c>
-      <c r="C53" s="7" t="inlineStr">
+      <c r="C54" s="7" t="inlineStr">
         <is>
           <t>シニアクラブうらら</t>
         </is>
       </c>
-      <c r="D53" s="7" t="inlineStr">
+      <c r="D54" s="7" t="inlineStr">
         <is>
           <t>シニアいきいきサロン</t>
         </is>
       </c>
-      <c r="E53" s="8" t="inlineStr">
+      <c r="E54" s="8" t="inlineStr">
         <is>
           <t>イ・会</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="9" t="n"/>
-      <c r="B54" s="6" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="9" t="n"/>
+      <c r="B55" s="6" t="inlineStr">
         <is>
           <t>13:20～17:10</t>
         </is>
       </c>
-      <c r="C54" s="7" t="inlineStr">
+      <c r="C55" s="7" t="inlineStr">
         <is>
           <t>楽しい健康吹き矢</t>
         </is>
       </c>
-      <c r="D54" s="7" t="inlineStr">
+      <c r="D55" s="7" t="inlineStr">
         <is>
           <t>吹矢を楽しむ</t>
         </is>
       </c>
-      <c r="E54" s="8" t="inlineStr">
-        <is>
-          <t>会</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>会</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>10月31日（土）</t>
         </is>
       </c>
-      <c r="B55" s="6" t="inlineStr">
+      <c r="B56" s="6" t="inlineStr">
         <is>
           <t>10:00～11:30</t>
         </is>
       </c>
-      <c r="C55" s="7" t="inlineStr">
+      <c r="C56" s="7" t="inlineStr">
         <is>
           <t>パレアひばりの会</t>
         </is>
       </c>
-      <c r="D55" s="7" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr">
         <is>
           <t>フリートーキング</t>
-        </is>
-      </c>
-      <c r="E55" s="8" t="inlineStr">
-        <is>
-          <t>イ</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="10" t="n"/>
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>14:00～15:00</t>
-        </is>
-      </c>
-      <c r="C56" s="7" t="inlineStr">
-        <is>
-          <t>英会話サークルGreenGables</t>
-        </is>
-      </c>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>英会話サロン</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
@@ -1811,140 +1811,140 @@
       <c r="A57" s="10" t="n"/>
       <c r="B57" s="6" t="inlineStr">
         <is>
+          <t>14:00～15:00</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>英会話サークルGreenGables</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>英会話サロン</t>
+        </is>
+      </c>
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t>イ</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="n"/>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
           <t>10:00～12:30</t>
         </is>
       </c>
-      <c r="C57" s="7" t="inlineStr">
+      <c r="C58" s="7" t="inlineStr">
         <is>
           <t>特定非営利活動法人 教育支援プロジェクトマスターズ熊本</t>
         </is>
       </c>
-      <c r="D57" s="7" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr">
         <is>
           <t>親と子の成長を応援　親子多肉寄せ植えとリメイク鉢セミナー</t>
         </is>
       </c>
-      <c r="E57" s="8" t="inlineStr">
-        <is>
-          <t>会</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="9" t="n"/>
-      <c r="B58" s="6" t="inlineStr">
+      <c r="E58" s="8" t="inlineStr">
+        <is>
+          <t>会</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="n"/>
+      <c r="B59" s="6" t="inlineStr">
         <is>
           <t>14:00～17:00</t>
         </is>
       </c>
-      <c r="C58" s="7" t="inlineStr">
+      <c r="C59" s="7" t="inlineStr">
         <is>
           <t>熊本生と死を考える会</t>
         </is>
       </c>
-      <c r="D58" s="7" t="inlineStr">
+      <c r="D59" s="7" t="inlineStr">
         <is>
           <t>熊本生と死を考える会</t>
         </is>
       </c>
-      <c r="E58" s="8" t="inlineStr">
-        <is>
-          <t>会</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
+      <c r="E59" s="8" t="inlineStr">
+        <is>
+          <t>会</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
         <is>
           <t>11月1日（日）</t>
         </is>
       </c>
-      <c r="B59" s="6" t="inlineStr">
+      <c r="B60" s="6" t="inlineStr">
         <is>
           <t>13:40～16:30</t>
         </is>
       </c>
-      <c r="C59" s="7" t="inlineStr">
+      <c r="C60" s="7" t="inlineStr">
         <is>
           <t>ラジオ英語の会</t>
         </is>
       </c>
-      <c r="D59" s="7" t="inlineStr">
+      <c r="D60" s="7" t="inlineStr">
         <is>
           <t>英語を楽しもう</t>
         </is>
       </c>
-      <c r="E59" s="8" t="inlineStr">
-        <is>
-          <t>イ</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="9" t="n"/>
-      <c r="B60" s="6" t="inlineStr">
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>イ</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="9" t="n"/>
+      <c r="B61" s="6" t="inlineStr">
         <is>
           <t>14:00～16:30</t>
         </is>
       </c>
-      <c r="C60" s="7" t="inlineStr">
+      <c r="C61" s="7" t="inlineStr">
         <is>
           <t>ブレーメンの音楽隊</t>
         </is>
       </c>
-      <c r="D60" s="7" t="inlineStr">
+      <c r="D61" s="7" t="inlineStr">
         <is>
           <t>音楽を楽しむ</t>
         </is>
       </c>
-      <c r="E60" s="8" t="inlineStr">
-        <is>
-          <t>会</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t>会</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
         <is>
           <t>11月2日（月）</t>
         </is>
       </c>
-      <c r="B61" s="6" t="inlineStr">
+      <c r="B62" s="6" t="inlineStr">
         <is>
           <t>10:00～11:50</t>
         </is>
       </c>
-      <c r="C61" s="7" t="inlineStr">
+      <c r="C62" s="7" t="inlineStr">
         <is>
           <t>ヨガ健康クラブ</t>
         </is>
       </c>
-      <c r="D61" s="7" t="inlineStr">
+      <c r="D62" s="7" t="inlineStr">
         <is>
           <t>ヨガ入門</t>
-        </is>
-      </c>
-      <c r="E61" s="8" t="inlineStr">
-        <is>
-          <t>イ</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="10" t="n"/>
-      <c r="B62" s="6" t="inlineStr">
-        <is>
-          <t>12:00～15:00</t>
-        </is>
-      </c>
-      <c r="C62" s="7" t="inlineStr">
-        <is>
-          <t>フラ・オ・レアレア</t>
-        </is>
-      </c>
-      <c r="D62" s="7" t="inlineStr">
-        <is>
-          <t>フラダンスレッスン</t>
         </is>
       </c>
       <c r="E62" s="8" t="inlineStr">
@@ -1957,17 +1957,17 @@
       <c r="A63" s="10" t="n"/>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>18:30～20:30</t>
+          <t>12:00～15:00</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>マイカ</t>
+          <t>フラ・オ・レアレア</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>フォークダンス</t>
+          <t>フラダンスレッスン</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
@@ -1980,22 +1980,22 @@
       <c r="A64" s="10" t="n"/>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>10:00～11:50</t>
+          <t>18:30～20:30</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>さわやかボランティアーズ４班</t>
+          <t>マイカ</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>さわやかボランティアーズ４班打合せ</t>
+          <t>フォークダンス</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>会</t>
+          <t>イ</t>
         </is>
       </c>
     </row>
@@ -2003,90 +2003,90 @@
       <c r="A65" s="10" t="n"/>
       <c r="B65" s="6" t="inlineStr">
         <is>
+          <t>10:00～11:50</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>さわやかボランティアーズ４班</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>さわやかボランティアーズ４班打合せ</t>
+        </is>
+      </c>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>会</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="n"/>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
           <t>14:00～15:30</t>
         </is>
       </c>
-      <c r="C65" s="7" t="inlineStr">
+      <c r="C66" s="7" t="inlineStr">
         <is>
           <t>ピエロン教室</t>
         </is>
       </c>
-      <c r="D65" s="7" t="inlineStr">
+      <c r="D66" s="7" t="inlineStr">
         <is>
           <t>マジックの練習</t>
         </is>
       </c>
-      <c r="E65" s="8" t="inlineStr">
-        <is>
-          <t>会</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="9" t="n"/>
-      <c r="B66" s="6" t="inlineStr">
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>会</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="9" t="n"/>
+      <c r="B67" s="6" t="inlineStr">
         <is>
           <t>17:20～20:30</t>
         </is>
       </c>
-      <c r="C66" s="7" t="inlineStr">
+      <c r="C67" s="7" t="inlineStr">
         <is>
           <t>楽しい健康吹き矢</t>
         </is>
       </c>
-      <c r="D66" s="7" t="inlineStr">
+      <c r="D67" s="7" t="inlineStr">
         <is>
           <t>吹矢を楽しむ</t>
         </is>
       </c>
-      <c r="E66" s="8" t="inlineStr">
-        <is>
-          <t>会</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>会</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
         <is>
           <t>11月3日（火）</t>
         </is>
       </c>
-      <c r="B67" s="6" t="inlineStr">
+      <c r="B68" s="6" t="inlineStr">
         <is>
           <t>12:30～17:30</t>
         </is>
       </c>
-      <c r="C67" s="7" t="inlineStr">
+      <c r="C68" s="7" t="inlineStr">
         <is>
           <t>囲碁普及会</t>
         </is>
       </c>
-      <c r="D67" s="7" t="inlineStr">
+      <c r="D68" s="7" t="inlineStr">
         <is>
           <t>囲碁の対局・初心者の指導と研究</t>
-        </is>
-      </c>
-      <c r="E67" s="8" t="inlineStr">
-        <is>
-          <t>イ</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="10" t="n"/>
-      <c r="B68" s="6" t="inlineStr">
-        <is>
-          <t>18:30～20:30</t>
-        </is>
-      </c>
-      <c r="C68" s="7" t="inlineStr">
-        <is>
-          <t>マイカ</t>
-        </is>
-      </c>
-      <c r="D68" s="7" t="inlineStr">
-        <is>
-          <t>フォークダンス</t>
         </is>
       </c>
       <c r="E68" s="8" t="inlineStr">
@@ -2099,236 +2099,236 @@
       <c r="A69" s="10" t="n"/>
       <c r="B69" s="6" t="inlineStr">
         <is>
+          <t>18:30～20:30</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>マイカ</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>フォークダンス</t>
+        </is>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>イ</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="n"/>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
           <t>9:30～11:30</t>
         </is>
       </c>
-      <c r="C69" s="7" t="inlineStr">
+      <c r="C70" s="7" t="inlineStr">
         <is>
           <t>楽しいオリガミ</t>
         </is>
       </c>
-      <c r="D69" s="7" t="inlineStr">
+      <c r="D70" s="7" t="inlineStr">
         <is>
           <t>折紙製作勉強会</t>
         </is>
       </c>
-      <c r="E69" s="8" t="inlineStr">
-        <is>
-          <t>会</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="9" t="n"/>
-      <c r="B70" s="6" t="inlineStr">
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t>会</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="n"/>
+      <c r="B71" s="6" t="inlineStr">
         <is>
           <t>13:00～15:00</t>
         </is>
       </c>
-      <c r="C70" s="7" t="inlineStr">
+      <c r="C71" s="7" t="inlineStr">
         <is>
           <t>NPO法人傾聴ネットキーステーション</t>
         </is>
       </c>
-      <c r="D70" s="7" t="inlineStr">
+      <c r="D71" s="7" t="inlineStr">
         <is>
           <t>27期傾聴ボランティア養成講座(1回目)</t>
         </is>
       </c>
-      <c r="E70" s="8" t="inlineStr">
-        <is>
-          <t>会</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="5" t="inlineStr">
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>会</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
         <is>
           <t>11月4日（水）</t>
         </is>
       </c>
-      <c r="B71" s="6" t="inlineStr">
+      <c r="B72" s="6" t="inlineStr">
         <is>
           <t>14:00～16:30</t>
         </is>
       </c>
-      <c r="C71" s="7" t="inlineStr">
+      <c r="C72" s="7" t="inlineStr">
         <is>
           <t>NPO法人でんでん虫の会</t>
         </is>
       </c>
-      <c r="D71" s="7" t="inlineStr">
+      <c r="D72" s="7" t="inlineStr">
         <is>
           <t>おしゃべり会</t>
         </is>
       </c>
-      <c r="E71" s="8" t="inlineStr">
-        <is>
-          <t>イ</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="10" t="n"/>
-      <c r="B72" s="6" t="inlineStr">
+      <c r="E72" s="8" t="inlineStr">
+        <is>
+          <t>イ</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="n"/>
+      <c r="B73" s="6" t="inlineStr">
         <is>
           <t>10:00～12:00</t>
         </is>
       </c>
-      <c r="C72" s="7" t="inlineStr">
+      <c r="C73" s="7" t="inlineStr">
         <is>
           <t>多胎サークル　ダブルハッピー</t>
         </is>
       </c>
-      <c r="D72" s="7" t="inlineStr">
+      <c r="D73" s="7" t="inlineStr">
         <is>
           <t>多胎サークル　ダブルハッピー</t>
         </is>
       </c>
-      <c r="E72" s="8" t="inlineStr">
-        <is>
-          <t>会</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="9" t="n"/>
-      <c r="B73" s="6" t="inlineStr">
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>会</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="9" t="n"/>
+      <c r="B74" s="6" t="inlineStr">
         <is>
           <t>13:10～15:50</t>
         </is>
       </c>
-      <c r="C73" s="7" t="inlineStr">
+      <c r="C74" s="7" t="inlineStr">
         <is>
           <t>楽画喜の会</t>
         </is>
       </c>
-      <c r="D73" s="7" t="inlineStr">
+      <c r="D74" s="7" t="inlineStr">
         <is>
           <t>絵画制作活動</t>
         </is>
       </c>
-      <c r="E73" s="8" t="inlineStr">
-        <is>
-          <t>会</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="5" t="inlineStr">
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>会</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
         <is>
           <t>11月5日（木）</t>
         </is>
       </c>
-      <c r="B74" s="6" t="inlineStr">
+      <c r="B75" s="6" t="inlineStr">
         <is>
           <t>12:30～14:30</t>
         </is>
       </c>
-      <c r="C74" s="7" t="inlineStr">
+      <c r="C75" s="7" t="inlineStr">
         <is>
           <t>懐かしい盆踊りの会</t>
         </is>
       </c>
-      <c r="D74" s="7" t="inlineStr">
+      <c r="D75" s="7" t="inlineStr">
         <is>
           <t>懐かしい盆踊りのボランティア会の打合せ、練習</t>
         </is>
       </c>
-      <c r="E74" s="8" t="inlineStr">
-        <is>
-          <t>イ</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="10" t="n"/>
-      <c r="B75" s="6" t="inlineStr">
+      <c r="E75" s="8" t="inlineStr">
+        <is>
+          <t>イ</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="n"/>
+      <c r="B76" s="6" t="inlineStr">
         <is>
           <t>10:00～17:00</t>
         </is>
       </c>
-      <c r="C75" s="7" t="inlineStr">
+      <c r="C76" s="7" t="inlineStr">
         <is>
           <t>スマイリー健＆アロハ・スターハワイアンズ</t>
         </is>
       </c>
-      <c r="D75" s="7" t="inlineStr">
+      <c r="D76" s="7" t="inlineStr">
         <is>
           <t>ウクレレを楽しもう♪</t>
         </is>
       </c>
-      <c r="E75" s="8" t="inlineStr">
-        <is>
-          <t>会</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="9" t="n"/>
-      <c r="B76" s="6" t="inlineStr">
+      <c r="E76" s="8" t="inlineStr">
+        <is>
+          <t>会</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="9" t="n"/>
+      <c r="B77" s="6" t="inlineStr">
         <is>
           <t>18:30～20:30</t>
         </is>
       </c>
-      <c r="C76" s="7" t="inlineStr">
+      <c r="C77" s="7" t="inlineStr">
         <is>
           <t>熊本フォークダンスクラブ</t>
         </is>
       </c>
-      <c r="D76" s="7" t="inlineStr">
+      <c r="D77" s="7" t="inlineStr">
         <is>
           <t>フォークダンス練習会</t>
         </is>
       </c>
-      <c r="E76" s="8" t="inlineStr">
-        <is>
-          <t>会</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="5" t="inlineStr">
+      <c r="E77" s="8" t="inlineStr">
+        <is>
+          <t>会</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
         <is>
           <t>11月6日（金）</t>
         </is>
       </c>
-      <c r="B77" s="6" t="inlineStr">
+      <c r="B78" s="6" t="inlineStr">
         <is>
           <t>9:30～12:30</t>
         </is>
       </c>
-      <c r="C77" s="7" t="inlineStr">
+      <c r="C78" s="7" t="inlineStr">
         <is>
           <t>シニアクラブうらら</t>
         </is>
       </c>
-      <c r="D77" s="7" t="inlineStr">
+      <c r="D78" s="7" t="inlineStr">
         <is>
           <t>シニアいきいきサロン</t>
-        </is>
-      </c>
-      <c r="E77" s="8" t="inlineStr">
-        <is>
-          <t>イ</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="10" t="n"/>
-      <c r="B78" s="6" t="inlineStr">
-        <is>
-          <t>13:30～15:30</t>
-        </is>
-      </c>
-      <c r="C78" s="7" t="inlineStr">
-        <is>
-          <t>NPO法人熊本わくわく体操ボランティア協会</t>
-        </is>
-      </c>
-      <c r="D78" s="7" t="inlineStr">
-        <is>
-          <t>いつでも・だれでも健康体操</t>
         </is>
       </c>
       <c r="E78" s="8" t="inlineStr">
@@ -2341,240 +2341,240 @@
       <c r="A79" s="10" t="n"/>
       <c r="B79" s="6" t="inlineStr">
         <is>
+          <t>13:30～15:30</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>NPO法人熊本わくわく体操ボランティア協会</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>いつでも・だれでも健康体操</t>
+        </is>
+      </c>
+      <c r="E79" s="8" t="inlineStr">
+        <is>
+          <t>イ</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="10" t="n"/>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
           <t>10:00～11:30</t>
         </is>
       </c>
-      <c r="C79" s="7" t="inlineStr">
+      <c r="C80" s="7" t="inlineStr">
         <is>
           <t>熊本健康マージャン協会</t>
         </is>
       </c>
-      <c r="D79" s="7" t="inlineStr">
+      <c r="D80" s="7" t="inlineStr">
         <is>
           <t>マージャン協会の座談会</t>
         </is>
       </c>
-      <c r="E79" s="8" t="inlineStr">
-        <is>
-          <t>会</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="9" t="n"/>
-      <c r="B80" s="6" t="inlineStr">
+      <c r="E80" s="8" t="inlineStr">
+        <is>
+          <t>会</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="9" t="n"/>
+      <c r="B81" s="6" t="inlineStr">
         <is>
           <t>14:30～17:30</t>
         </is>
       </c>
-      <c r="C80" s="7" t="inlineStr">
+      <c r="C81" s="7" t="inlineStr">
         <is>
           <t>スマイリー健＆アロハ・スターハワイアンズ</t>
         </is>
       </c>
-      <c r="D80" s="7" t="inlineStr">
+      <c r="D81" s="7" t="inlineStr">
         <is>
           <t>♪ハワイアン・懐メロ演奏会♪</t>
         </is>
       </c>
-      <c r="E80" s="8" t="inlineStr">
-        <is>
-          <t>会</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
+      <c r="E81" s="8" t="inlineStr">
+        <is>
+          <t>会</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
         <is>
           <t>11月7日（土）</t>
         </is>
       </c>
-      <c r="B81" s="6" t="inlineStr">
+      <c r="B82" s="6" t="inlineStr">
         <is>
           <t>13:30～16:30</t>
         </is>
       </c>
-      <c r="C81" s="7" t="inlineStr">
+      <c r="C82" s="7" t="inlineStr">
         <is>
           <t>東教養囲碁研究会</t>
         </is>
       </c>
-      <c r="D81" s="7" t="inlineStr">
+      <c r="D82" s="7" t="inlineStr">
         <is>
           <t>囲碁による人間形成・修練</t>
         </is>
       </c>
-      <c r="E81" s="8" t="inlineStr">
-        <is>
-          <t>イ</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="10" t="n"/>
-      <c r="B82" s="6" t="inlineStr">
+      <c r="E82" s="8" t="inlineStr">
+        <is>
+          <t>イ</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="n"/>
+      <c r="B83" s="6" t="inlineStr">
         <is>
           <t>10:00～13:00</t>
         </is>
       </c>
-      <c r="C82" s="7" t="inlineStr">
+      <c r="C83" s="7" t="inlineStr">
         <is>
           <t>特定非営利活動法人教育支援プロジェクトマスターズ熊本</t>
         </is>
       </c>
-      <c r="D82" s="7" t="inlineStr">
+      <c r="D83" s="7" t="inlineStr">
         <is>
           <t>教育支援プロジェクトマスターズ熊本20周年記念事業</t>
         </is>
       </c>
-      <c r="E82" s="8" t="inlineStr">
-        <is>
-          <t>会</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="9" t="n"/>
-      <c r="B83" s="6" t="inlineStr">
+      <c r="E83" s="8" t="inlineStr">
+        <is>
+          <t>会</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="9" t="n"/>
+      <c r="B84" s="6" t="inlineStr">
         <is>
           <t>13:30～16:30</t>
         </is>
       </c>
-      <c r="C83" s="7" t="inlineStr">
+      <c r="C84" s="7" t="inlineStr">
         <is>
           <t>傾聴ボランティアくまもと</t>
         </is>
       </c>
-      <c r="D83" s="7" t="inlineStr">
+      <c r="D84" s="7" t="inlineStr">
         <is>
           <t>傾聴定例会</t>
         </is>
       </c>
-      <c r="E83" s="8" t="inlineStr">
-        <is>
-          <t>会</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="5" t="inlineStr">
+      <c r="E84" s="8" t="inlineStr">
+        <is>
+          <t>会</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
         <is>
           <t>11月8日（日）</t>
         </is>
       </c>
-      <c r="B84" s="6" t="inlineStr">
+      <c r="B85" s="6" t="inlineStr">
         <is>
           <t>10:00～12:00</t>
         </is>
       </c>
-      <c r="C84" s="7" t="inlineStr">
+      <c r="C85" s="7" t="inlineStr">
         <is>
           <t>さわやか南京玉すだれを楽しむ会</t>
         </is>
       </c>
-      <c r="D84" s="7" t="inlineStr">
+      <c r="D85" s="7" t="inlineStr">
         <is>
           <t>南京玉すだれの練習</t>
         </is>
       </c>
-      <c r="E84" s="8" t="inlineStr">
-        <is>
-          <t>イ</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="9" t="n"/>
-      <c r="B85" s="6" t="inlineStr">
+      <c r="E85" s="8" t="inlineStr">
+        <is>
+          <t>イ</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="9" t="n"/>
+      <c r="B86" s="6" t="inlineStr">
         <is>
           <t>10:00～11:10</t>
         </is>
       </c>
-      <c r="C85" s="7" t="inlineStr">
+      <c r="C86" s="7" t="inlineStr">
         <is>
           <t>口からの健康づくり 歯っぴーかむカム</t>
         </is>
       </c>
-      <c r="D85" s="7" t="inlineStr">
+      <c r="D86" s="7" t="inlineStr">
         <is>
           <t>ベロタッチ生活養生・食養生</t>
         </is>
       </c>
-      <c r="E85" s="8" t="inlineStr">
-        <is>
-          <t>会</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="5" t="inlineStr">
-        <is>
-          <t>11月9日（月）</t>
-        </is>
-      </c>
-      <c r="B86" s="6" t="inlineStr">
-        <is>
-          <t>18:30～20:30</t>
-        </is>
-      </c>
-      <c r="C86" s="7" t="inlineStr">
-        <is>
-          <t>マイカ</t>
-        </is>
-      </c>
-      <c r="D86" s="7" t="inlineStr">
-        <is>
-          <t>フォークダンス</t>
-        </is>
-      </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>イ</t>
+          <t>会</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
+          <t>11月9日（月）</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>18:30～20:30</t>
+        </is>
+      </c>
+      <c r="C87" s="7" t="inlineStr">
+        <is>
+          <t>マイカ</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>フォークダンス</t>
+        </is>
+      </c>
+      <c r="E87" s="8" t="inlineStr">
+        <is>
+          <t>イ</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
           <t>11月10日（火）</t>
         </is>
       </c>
-      <c r="B87" s="6" t="inlineStr">
+      <c r="B88" s="6" t="inlineStr">
         <is>
           <t>9:30～12:00</t>
         </is>
       </c>
-      <c r="C87" s="7" t="inlineStr">
+      <c r="C88" s="7" t="inlineStr">
         <is>
           <t>はなの風</t>
         </is>
       </c>
-      <c r="D87" s="7" t="inlineStr">
+      <c r="D88" s="7" t="inlineStr">
         <is>
           <t>はなの風（水彩画教室）</t>
-        </is>
-      </c>
-      <c r="E87" s="8" t="inlineStr">
-        <is>
-          <t>イ</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="10" t="n"/>
-      <c r="B88" s="6" t="inlineStr">
-        <is>
-          <t>12:30～17:30</t>
-        </is>
-      </c>
-      <c r="C88" s="7" t="inlineStr">
-        <is>
-          <t>囲碁普及会</t>
-        </is>
-      </c>
-      <c r="D88" s="7" t="inlineStr">
-        <is>
-          <t>囲碁の対局・初心者の指導と研究</t>
         </is>
       </c>
       <c r="E88" s="8" t="inlineStr">
@@ -2587,17 +2587,17 @@
       <c r="A89" s="10" t="n"/>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>19:00～20:30</t>
+          <t>12:30～17:30</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>熊本市キャンプ協会</t>
+          <t>囲碁普及会</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>定例会</t>
+          <t>囲碁の対局・初心者の指導と研究</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
@@ -2610,22 +2610,22 @@
       <c r="A90" s="10" t="n"/>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>10:00～12:00</t>
+          <t>19:00～20:30</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>太極拳を楽しもう会</t>
+          <t>熊本市キャンプ協会</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>健康太極拳</t>
+          <t>定例会</t>
         </is>
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>会</t>
+          <t>イ</t>
         </is>
       </c>
     </row>
@@ -2633,90 +2633,90 @@
       <c r="A91" s="10" t="n"/>
       <c r="B91" s="6" t="inlineStr">
         <is>
+          <t>10:00～12:00</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>太極拳を楽しもう会</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>健康太極拳</t>
+        </is>
+      </c>
+      <c r="E91" s="8" t="inlineStr">
+        <is>
+          <t>会</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="10" t="n"/>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
           <t>13:00～15:00</t>
         </is>
       </c>
-      <c r="C91" s="7" t="inlineStr">
+      <c r="C92" s="7" t="inlineStr">
         <is>
           <t>NPO法人傾聴ネットキーステーション</t>
         </is>
       </c>
-      <c r="D91" s="7" t="inlineStr">
+      <c r="D92" s="7" t="inlineStr">
         <is>
           <t>27期傾聴ボランティア養成講座(2回目)</t>
         </is>
       </c>
-      <c r="E91" s="8" t="inlineStr">
-        <is>
-          <t>会</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="9" t="n"/>
-      <c r="B92" s="6" t="inlineStr">
+      <c r="E92" s="8" t="inlineStr">
+        <is>
+          <t>会</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="9" t="n"/>
+      <c r="B93" s="6" t="inlineStr">
         <is>
           <t>19:30～20:30</t>
         </is>
       </c>
-      <c r="C92" s="7" t="inlineStr">
+      <c r="C93" s="7" t="inlineStr">
         <is>
           <t>笑顔のたまて箱</t>
         </is>
       </c>
-      <c r="D92" s="7" t="inlineStr">
+      <c r="D93" s="7" t="inlineStr">
         <is>
           <t>人形劇の練習及び打合せ</t>
         </is>
       </c>
-      <c r="E92" s="8" t="inlineStr">
-        <is>
-          <t>会</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="5" t="inlineStr">
+      <c r="E93" s="8" t="inlineStr">
+        <is>
+          <t>会</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
         <is>
           <t>11月11日（水）</t>
         </is>
       </c>
-      <c r="B93" s="6" t="inlineStr">
+      <c r="B94" s="6" t="inlineStr">
         <is>
           <t>9:40～11:30</t>
         </is>
       </c>
-      <c r="C93" s="7" t="inlineStr">
+      <c r="C94" s="7" t="inlineStr">
         <is>
           <t>KKA高齢者健康友の会</t>
         </is>
       </c>
-      <c r="D93" s="7" t="inlineStr">
+      <c r="D94" s="7" t="inlineStr">
         <is>
           <t>みんな笑顔で楽しく健康体操</t>
-        </is>
-      </c>
-      <c r="E93" s="8" t="inlineStr">
-        <is>
-          <t>イ</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="10" t="n"/>
-      <c r="B94" s="6" t="inlineStr">
-        <is>
-          <t>10:00～12:00</t>
-        </is>
-      </c>
-      <c r="C94" s="7" t="inlineStr">
-        <is>
-          <t>（一社）熊本県助産師会</t>
-        </is>
-      </c>
-      <c r="D94" s="7" t="inlineStr">
-        <is>
-          <t>ママ＆ベビー教室</t>
         </is>
       </c>
       <c r="E94" s="8" t="inlineStr">
@@ -2729,90 +2729,90 @@
       <c r="A95" s="10" t="n"/>
       <c r="B95" s="6" t="inlineStr">
         <is>
+          <t>10:00～12:00</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>（一社）熊本県助産師会</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>ママ＆ベビー教室</t>
+        </is>
+      </c>
+      <c r="E95" s="8" t="inlineStr">
+        <is>
+          <t>イ</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="10" t="n"/>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
           <t>14:00～16:30</t>
         </is>
       </c>
-      <c r="C95" s="7" t="inlineStr">
+      <c r="C96" s="7" t="inlineStr">
         <is>
           <t>NPO法人でんでん虫の会</t>
         </is>
       </c>
-      <c r="D95" s="7" t="inlineStr">
+      <c r="D96" s="7" t="inlineStr">
         <is>
           <t>おしゃべり会</t>
         </is>
       </c>
-      <c r="E95" s="8" t="inlineStr">
-        <is>
-          <t>イ</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="9" t="n"/>
-      <c r="B96" s="6" t="inlineStr">
+      <c r="E96" s="8" t="inlineStr">
+        <is>
+          <t>イ</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="9" t="n"/>
+      <c r="B97" s="6" t="inlineStr">
         <is>
           <t>13:30～17:30</t>
         </is>
       </c>
-      <c r="C96" s="7" t="inlineStr">
+      <c r="C97" s="7" t="inlineStr">
         <is>
           <t>「アミーゴ」</t>
         </is>
       </c>
-      <c r="D96" s="7" t="inlineStr">
+      <c r="D97" s="7" t="inlineStr">
         <is>
           <t>「アミーゴ」バンド活動</t>
         </is>
       </c>
-      <c r="E96" s="8" t="inlineStr">
-        <is>
-          <t>会</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="5" t="inlineStr">
+      <c r="E97" s="8" t="inlineStr">
+        <is>
+          <t>会</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
         <is>
           <t>11月13日（金）</t>
         </is>
       </c>
-      <c r="B97" s="6" t="inlineStr">
+      <c r="B98" s="6" t="inlineStr">
         <is>
           <t>13:00～17:30</t>
         </is>
       </c>
-      <c r="C97" s="7" t="inlineStr">
+      <c r="C98" s="7" t="inlineStr">
         <is>
           <t>囲碁普及会</t>
         </is>
       </c>
-      <c r="D97" s="7" t="inlineStr">
+      <c r="D98" s="7" t="inlineStr">
         <is>
           <t>囲碁の研究と対局</t>
-        </is>
-      </c>
-      <c r="E97" s="8" t="inlineStr">
-        <is>
-          <t>イ</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="10" t="n"/>
-      <c r="B98" s="6" t="inlineStr">
-        <is>
-          <t>18:30～20:30</t>
-        </is>
-      </c>
-      <c r="C98" s="7" t="inlineStr">
-        <is>
-          <t>一般社団法人アイ・オー・イー（IOE）</t>
-        </is>
-      </c>
-      <c r="D98" s="7" t="inlineStr">
-        <is>
-          <t>くまもとNPOカレッジ2026</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
@@ -2825,22 +2825,22 @@
       <c r="A99" s="10" t="n"/>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>9:30～12:30</t>
+          <t>18:30～20:30</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>シニアクラブうらら</t>
+          <t>一般社団法人アイ・オー・イー（IOE）</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>シニアいきいきサロン</t>
+          <t>くまもとNPOカレッジ2026</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>会</t>
+          <t>イ</t>
         </is>
       </c>
     </row>
@@ -2848,90 +2848,90 @@
       <c r="A100" s="10" t="n"/>
       <c r="B100" s="6" t="inlineStr">
         <is>
+          <t>9:30～12:30</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="inlineStr">
+        <is>
+          <t>シニアクラブうらら</t>
+        </is>
+      </c>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
+          <t>シニアいきいきサロン</t>
+        </is>
+      </c>
+      <c r="E100" s="8" t="inlineStr">
+        <is>
+          <t>会</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="10" t="n"/>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
           <t>12:30～17:00</t>
         </is>
       </c>
-      <c r="C100" s="7" t="inlineStr">
+      <c r="C101" s="7" t="inlineStr">
         <is>
           <t>AA九州・沖縄地域熊本地区</t>
         </is>
       </c>
-      <c r="D100" s="7" t="inlineStr">
+      <c r="D101" s="7" t="inlineStr">
         <is>
           <t>AA九州・沖縄地域 矯正・保護施設フォーラムin熊本</t>
         </is>
       </c>
-      <c r="E100" s="8" t="inlineStr">
-        <is>
-          <t>会</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="9" t="n"/>
-      <c r="B101" s="6" t="inlineStr">
+      <c r="E101" s="8" t="inlineStr">
+        <is>
+          <t>会</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="9" t="n"/>
+      <c r="B102" s="6" t="inlineStr">
         <is>
           <t>18:30～20:30</t>
         </is>
       </c>
-      <c r="C101" s="7" t="inlineStr">
+      <c r="C102" s="7" t="inlineStr">
         <is>
           <t>熊本フォークダンスクラブ</t>
         </is>
       </c>
-      <c r="D101" s="7" t="inlineStr">
+      <c r="D102" s="7" t="inlineStr">
         <is>
           <t>フォークダンス練習会</t>
         </is>
       </c>
-      <c r="E101" s="8" t="inlineStr">
-        <is>
-          <t>会</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="5" t="inlineStr">
+      <c r="E102" s="8" t="inlineStr">
+        <is>
+          <t>会</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
         <is>
           <t>11月14日（土）</t>
         </is>
       </c>
-      <c r="B102" s="6" t="inlineStr">
+      <c r="B103" s="6" t="inlineStr">
         <is>
           <t>9:00～11:50</t>
         </is>
       </c>
-      <c r="C102" s="7" t="inlineStr">
+      <c r="C103" s="7" t="inlineStr">
         <is>
           <t>熊本さわやかハイヤ俱楽部</t>
         </is>
       </c>
-      <c r="D102" s="7" t="inlineStr">
+      <c r="D103" s="7" t="inlineStr">
         <is>
           <t>熊本の郷土芸能「牛深ハイヤ踊り」の練習</t>
-        </is>
-      </c>
-      <c r="E102" s="8" t="inlineStr">
-        <is>
-          <t>イ</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="10" t="n"/>
-      <c r="B103" s="6" t="inlineStr">
-        <is>
-          <t>13:30～16:30</t>
-        </is>
-      </c>
-      <c r="C103" s="7" t="inlineStr">
-        <is>
-          <t>東教養囲碁研究会</t>
-        </is>
-      </c>
-      <c r="D103" s="7" t="inlineStr">
-        <is>
-          <t>囲碁による人間形成・修練</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
@@ -2944,90 +2944,90 @@
       <c r="A104" s="10" t="n"/>
       <c r="B104" s="6" t="inlineStr">
         <is>
+          <t>13:30～16:30</t>
+        </is>
+      </c>
+      <c r="C104" s="7" t="inlineStr">
+        <is>
+          <t>東教養囲碁研究会</t>
+        </is>
+      </c>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>囲碁による人間形成・修練</t>
+        </is>
+      </c>
+      <c r="E104" s="8" t="inlineStr">
+        <is>
+          <t>イ</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="10" t="n"/>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
           <t>9:00～11:50</t>
         </is>
       </c>
-      <c r="C104" s="7" t="inlineStr">
+      <c r="C105" s="7" t="inlineStr">
         <is>
           <t>熊本史談会</t>
         </is>
       </c>
-      <c r="D104" s="7" t="inlineStr">
+      <c r="D105" s="7" t="inlineStr">
         <is>
           <t>熊本歴史の勉強会</t>
         </is>
       </c>
-      <c r="E104" s="8" t="inlineStr">
-        <is>
-          <t>会</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="9" t="n"/>
-      <c r="B105" s="6" t="inlineStr">
+      <c r="E105" s="8" t="inlineStr">
+        <is>
+          <t>会</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="9" t="n"/>
+      <c r="B106" s="6" t="inlineStr">
         <is>
           <t>13:30～16:30</t>
         </is>
       </c>
-      <c r="C105" s="7" t="inlineStr">
+      <c r="C106" s="7" t="inlineStr">
         <is>
           <t>登校拒否・不登校に学ぶフレンズネットワークくまもと</t>
         </is>
       </c>
-      <c r="D105" s="7" t="inlineStr">
+      <c r="D106" s="7" t="inlineStr">
         <is>
           <t>フレンズ親の会</t>
         </is>
       </c>
-      <c r="E105" s="8" t="inlineStr">
-        <is>
-          <t>会</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="5" t="inlineStr">
+      <c r="E106" s="8" t="inlineStr">
+        <is>
+          <t>会</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
         <is>
           <t>11月15日（日）</t>
         </is>
       </c>
-      <c r="B106" s="6" t="inlineStr">
+      <c r="B107" s="6" t="inlineStr">
         <is>
           <t>9:00～12:30</t>
         </is>
       </c>
-      <c r="C106" s="7" t="inlineStr">
+      <c r="C107" s="7" t="inlineStr">
         <is>
           <t>特定非営利活動法人 教育支援プロジェクトマスターズ熊本</t>
         </is>
       </c>
-      <c r="D106" s="7" t="inlineStr">
+      <c r="D107" s="7" t="inlineStr">
         <is>
           <t>親と子の体験　クリスマスプレート作り(陶磁器)</t>
-        </is>
-      </c>
-      <c r="E106" s="8" t="inlineStr">
-        <is>
-          <t>イ</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="10" t="n"/>
-      <c r="B107" s="6" t="inlineStr">
-        <is>
-          <t>13:40～16:30</t>
-        </is>
-      </c>
-      <c r="C107" s="7" t="inlineStr">
-        <is>
-          <t>ラジオ英語の会</t>
-        </is>
-      </c>
-      <c r="D107" s="7" t="inlineStr">
-        <is>
-          <t>英語を楽しもう</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
@@ -3040,43 +3040,66 @@
       <c r="A108" s="10" t="n"/>
       <c r="B108" s="6" t="inlineStr">
         <is>
+          <t>13:40～16:30</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="inlineStr">
+        <is>
+          <t>ラジオ英語の会</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t>英語を楽しもう</t>
+        </is>
+      </c>
+      <c r="E108" s="8" t="inlineStr">
+        <is>
+          <t>イ</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="10" t="n"/>
+      <c r="B109" s="6" t="inlineStr">
+        <is>
           <t>11:00～12:00</t>
         </is>
       </c>
-      <c r="C108" s="7" t="inlineStr">
+      <c r="C109" s="7" t="inlineStr">
         <is>
           <t>くまもと琵琶楽普及会</t>
         </is>
       </c>
-      <c r="D108" s="7" t="inlineStr">
+      <c r="D109" s="7" t="inlineStr">
         <is>
           <t>ワークショップ 琵琶の音色を楽しむ</t>
         </is>
       </c>
-      <c r="E108" s="8" t="inlineStr">
-        <is>
-          <t>会</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="9" t="n"/>
-      <c r="B109" s="6" t="inlineStr">
+      <c r="E109" s="8" t="inlineStr">
+        <is>
+          <t>会</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="9" t="n"/>
+      <c r="B110" s="6" t="inlineStr">
         <is>
           <t>15:00～17:30</t>
         </is>
       </c>
-      <c r="C109" s="7" t="inlineStr">
+      <c r="C110" s="7" t="inlineStr">
         <is>
           <t>「アミーゴ」</t>
         </is>
       </c>
-      <c r="D109" s="7" t="inlineStr">
+      <c r="D110" s="7" t="inlineStr">
         <is>
           <t>高齢者バンド</t>
         </is>
       </c>
-      <c r="E109" s="8" t="inlineStr">
+      <c r="E110" s="8" t="inlineStr">
         <is>
           <t>会</t>
         </is>
@@ -3084,35 +3107,35 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="A67:A70"/>
-    <mergeCell ref="A48:A51"/>
-    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="A94:A97"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="A107:A110"/>
     <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A72:A74"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A81:A83"/>
-    <mergeCell ref="A97:A101"/>
-    <mergeCell ref="A61:A66"/>
+    <mergeCell ref="A78:A81"/>
+    <mergeCell ref="A103:A106"/>
+    <mergeCell ref="A53:A55"/>
+    <mergeCell ref="A88:A93"/>
     <mergeCell ref="A9:A13"/>
-    <mergeCell ref="A52:A54"/>
-    <mergeCell ref="A87:A92"/>
+    <mergeCell ref="A56:A59"/>
     <mergeCell ref="A28:A32"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="A55:A58"/>
+    <mergeCell ref="A85:A86"/>
     <mergeCell ref="A33:A36"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="A18:A23"/>
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A82:A84"/>
     <mergeCell ref="A42:A45"/>
+    <mergeCell ref="A98:A102"/>
     <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A93:A96"/>
-    <mergeCell ref="A106:A109"/>
-    <mergeCell ref="A102:A105"/>
-    <mergeCell ref="A74:A76"/>
-    <mergeCell ref="A59:A60"/>
-    <mergeCell ref="A77:A80"/>
-    <mergeCell ref="A71:A73"/>
+    <mergeCell ref="A75:A77"/>
+    <mergeCell ref="A68:A71"/>
+    <mergeCell ref="A46:A48"/>
     <mergeCell ref="A24:A27"/>
     <mergeCell ref="A37:A41"/>
+    <mergeCell ref="A49:A52"/>
+    <mergeCell ref="A62:A67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>

--- a/newsletter.xlsx
+++ b/newsletter.xlsx
@@ -142,8 +142,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E110"/>
+  <dimension ref="A1:E125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>あいぽーとカレンダー 10月（後半）～11月（前半）</t>
+          <t>あいぽーとカレンダー 11月（後半）～12月（前半）</t>
         </is>
       </c>
     </row>
@@ -570,60 +570,68 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>10月17日（土）</t>
+          <t>11月16日（月）</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>13:00～16:00</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr"/>
+          <t>10:00～11:50</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>ヨガ健康クラブ</t>
+        </is>
+      </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>くまもと学生ボランティアFESTA2026</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr"/>
+          <t>ヨガ入門</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>イ</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>10月18日（日）</t>
-        </is>
-      </c>
+      <c r="A6" s="9" t="n"/>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>10:00～15:00</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr"/>
+          <t>13:10～14:50</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>カフェてくてく会</t>
+        </is>
+      </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>あいぽーとFESTIVAL2026</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr"/>
+          <t>カフェ　てくてく会</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>イ</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>10月19日（月）</t>
-        </is>
-      </c>
+      <c r="A7" s="9" t="n"/>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>10:00～11:45</t>
+          <t>18:30～20:30</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>ヨガ健康クラブ</t>
+          <t>マイカ</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>ヨガ入門</t>
+          <t>フォークダンス</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -636,118 +644,118 @@
       <c r="A8" s="9" t="n"/>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>12:15～15:00</t>
+          <t>9:10～11:50</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>フラ・オ・レアレア</t>
+          <t>熊本県おかあさんコーラス連盟</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>フラダンスレッスン</t>
+          <t>熊本県おかあさんコーラス連盟　第11回運営委員会</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>イ</t>
+          <t>会</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>10月20日（火）</t>
-        </is>
-      </c>
+      <c r="A9" s="10" t="n"/>
       <c r="B9" s="6" t="inlineStr">
         <is>
+          <t>13:30～17:30</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>「アミーゴ」</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>「アミーゴ」バンド活動</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>会</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>11月17日（火）</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
           <t>9:30～11:30</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>世界の民族舞踊ペガサス</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>世界各地の民族の踊りを楽しもう(フォークダンス)</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>イ</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="n"/>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>イ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="n"/>
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>12:30～17:30</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>囲碁普及会</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>囲碁の対局・初心者の指導と研究</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>イ</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="n"/>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>10:00～12:00</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>太極拳を楽しもう会</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>健康太極拳</t>
-        </is>
-      </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>会</t>
+          <t>イ</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="n"/>
+      <c r="A12" s="9" t="n"/>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>13:00～18:00</t>
+          <t>18:30～20:30</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>「アミーゴ」</t>
+          <t>マイカ</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>高齢者バンド</t>
+          <t>フォークダンス</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>会</t>
+          <t>イ</t>
         </is>
       </c>
     </row>
@@ -755,17 +763,17 @@
       <c r="A13" s="9" t="n"/>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>19:30～20:30</t>
+          <t>9:10～11:50</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>笑顔のたまて箱</t>
+          <t>Hula Welina O Nā Pua Mālie</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>人形劇の練習及び打合せ</t>
+          <t>ミーテイング</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -775,29 +783,25 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>10月21日（水）</t>
-        </is>
-      </c>
+      <c r="A14" s="9" t="n"/>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>9:40～11:30</t>
+          <t>13:00～15:00</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>KKA高齢者健康友の会</t>
+          <t>NPO法人傾聴ネットキーステーション</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>みんな笑顔で楽しく健康体操</t>
+          <t>27期傾聴ボランティア養成講座(3回目)</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>イ</t>
+          <t>会</t>
         </is>
       </c>
     </row>
@@ -805,45 +809,49 @@
       <c r="A15" s="10" t="n"/>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>14:00～16:30</t>
+          <t>17:30～19:30</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>NPO法人でんでん虫の会</t>
+          <t>CDLE熊本</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>おしゃべり会</t>
+          <t>ＣＤＬＥ熊本　生成ＡＩハンズオン勉強会（第5回）</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>イ</t>
+          <t>会</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="n"/>
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>11月18日（水）</t>
+        </is>
+      </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>13:10～15:50</t>
+          <t>9:40～11:30</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>楽画喜の会</t>
+          <t>KKA高齢者健康友の会</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>絵画制作活動</t>
+          <t>みんな笑顔で楽しく健康体操</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>会</t>
+          <t>イ</t>
         </is>
       </c>
     </row>
@@ -851,72 +859,68 @@
       <c r="A17" s="9" t="n"/>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>17:00～20:00</t>
+          <t>13:10～15:50</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>一般社団法人地域再生・百年ライフサポート協会羅針盤</t>
+          <t>楽画喜の会</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>相続遺言終活全般無料相談会及び研修会</t>
+          <t>絵画制作活動</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>会</t>
+          <t>イ</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>10月22日（木）</t>
-        </is>
-      </c>
+      <c r="A18" s="9" t="n"/>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>10:00～12:00</t>
+          <t>10:00～11:50</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>（一社）熊本県助産師会</t>
+          <t>熊本市居住支援協議会</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>ママ＆ベビー教室</t>
+          <t>あんしん住み替え相談会</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>イ</t>
+          <t>会</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="n"/>
+      <c r="A19" s="9" t="n"/>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>10:00～12:00</t>
+          <t>14:00～16:30</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>（一社）熊本県助産師会</t>
+          <t>ブレーメンの音楽隊</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>プレパパママ教室</t>
+          <t>音楽を楽しむ</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>イ</t>
+          <t>会</t>
         </is>
       </c>
     </row>
@@ -924,40 +928,44 @@
       <c r="A20" s="10" t="n"/>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>13:30～15:00</t>
+          <t>17:30～20:20</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>熊本さわやか大学校20期「絆２０会」</t>
+          <t>一般社団法人地域再生・百年ライフサポート協会羅針盤</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>健康体操教室</t>
+          <t>相続遺言終活全般無料相談会及び</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>イ</t>
+          <t>会</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="n"/>
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>11月19日（木）</t>
+        </is>
+      </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>16:15～19:45</t>
+          <t>10:00～12:00</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>fit(0-0)フィットれいわ</t>
+          <t>NPO法人傾聴ネットキーステーション</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>写真整理でコミュニケーション作り</t>
+          <t>傾聴カフェ「花ことば」</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
@@ -967,25 +975,25 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="n"/>
+      <c r="A22" s="9" t="n"/>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>10:00～15:00</t>
+          <t>13:00～16:00</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>NPO法人成年後見安心サポートネット熊本</t>
+          <t>フラ・オ・レアレア</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>成年後見無料相談会</t>
+          <t>フラダンスレッスン</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>会</t>
+          <t>イ</t>
         </is>
       </c>
     </row>
@@ -993,69 +1001,69 @@
       <c r="A23" s="9" t="n"/>
       <c r="B23" s="6" t="inlineStr">
         <is>
+          <t>10:00～17:00</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>スマイリー健＆アロハ・スターハワイアンズ</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>ウクレレを楽しもう♪</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>会</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n"/>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
           <t>18:30～20:30</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>熊本フォークダンスクラブ</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>フォークダンス練習会</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>会</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>10月23日（金）</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>会</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>11月20日（金）</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>9:30～12:30</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>シニアクラブうらら</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>シニアいきいきサロン</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t>イ</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="n"/>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>13:00～17:30</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>囲碁普及会</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>囲碁の研究と対局</t>
-        </is>
-      </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
           <t>イ</t>
@@ -1063,25 +1071,25 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="n"/>
+      <c r="A26" s="9" t="n"/>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>10:00～11:30</t>
+          <t>13:30～15:30</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>熊本健康マージャン協会</t>
+          <t>NPO法人熊本わくわく体操ボランティア協会</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>マージャン協会の座談会の打合せ</t>
+          <t>いつでも・だれでも健康体操</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>会</t>
+          <t>イ</t>
         </is>
       </c>
     </row>
@@ -1089,49 +1097,45 @@
       <c r="A27" s="9" t="n"/>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>13:20～15:30</t>
+          <t>9:30～12:30</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>エンジョイズ</t>
+          <t>シニアクラブうらら</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>童謡・唱歌・懐かしい流行歌を楽しむ会</t>
+          <t>シニアいきいきサロン</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>会</t>
+          <t>イ・会</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>10月24日（土）</t>
-        </is>
-      </c>
+      <c r="A28" s="9" t="n"/>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>10:30～12:00</t>
+          <t>13:10～13:50</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>ほっとステージBINGO</t>
+          <t>スマイリー健＆アロハ・スターハワイアンズ</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>ベビーマッサージ教室</t>
+          <t>♪ハワイアン・懐メロ演奏会♪</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>イ</t>
+          <t>会</t>
         </is>
       </c>
     </row>
@@ -1139,40 +1143,44 @@
       <c r="A29" s="10" t="n"/>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>13:00～15:50</t>
+          <t>14:30～17:30</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>熊本さわやかハイヤ俱楽部</t>
+          <t>スマイリー健＆アロハ・スターハワイアンズ</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>熊本の郷土芸能「牛深ハイヤ踊り」の練習</t>
+          <t>♪ハワイアン・懐メロ演奏会♪</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>イ</t>
+          <t>会</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="n"/>
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>11月21日（土）</t>
+        </is>
+      </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>17:00～19:00</t>
+          <t>10:30～12:00</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>一般社団法人 日本版DBS・BCP支援協会</t>
+          <t>ほっとステージBINGO</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>こども性暴力防止法の概要説明</t>
+          <t>ベビーマッサージ教室</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
@@ -1182,25 +1190,25 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="n"/>
+      <c r="A31" s="9" t="n"/>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>10:00～12:00</t>
+          <t>13:30～16:30</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>NPO法人成年後見安心サポートネット熊本</t>
+          <t>東教養囲碁研究会</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>後見実務研究会</t>
+          <t>囲碁による人間形成・修練</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>会</t>
+          <t>イ</t>
         </is>
       </c>
     </row>
@@ -1208,17 +1216,17 @@
       <c r="A32" s="9" t="n"/>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>13:30～16:30</t>
+          <t>10:00～12:00</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>東教養囲碁研究会</t>
+          <t>NPO法人成年後見安心サポートネット熊本</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>囲碁による人間形成・修練</t>
+          <t>成年後見無料相談会</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
@@ -1228,49 +1236,49 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>10月25日（日）</t>
-        </is>
-      </c>
+      <c r="A33" s="10" t="n"/>
       <c r="B33" s="6" t="inlineStr">
         <is>
+          <t>14:00～17:00</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>熊本・生と死を考える会</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>熊本・生と死を考える会例会</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>会</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>11月22日（日）</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
           <t>10:00～12:00</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>（一社）熊本県助産師会</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>プレパパママ教室</t>
         </is>
       </c>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t>イ</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="10" t="n"/>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>17:15～20:30</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>fit(0-0)フィットれいわ</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>写真整理で交流会</t>
-        </is>
-      </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
           <t>イ</t>
@@ -1278,25 +1286,25 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="n"/>
+      <c r="A35" s="9" t="n"/>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>10:00～13:00</t>
+          <t>13:40～16:30</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>熊日童話会</t>
+          <t>ラジオ英語の会</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>熊日童話会「口演教室、月例童話会」</t>
+          <t>英語を楽しもう</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>会</t>
+          <t>イ</t>
         </is>
       </c>
     </row>
@@ -1304,136 +1312,136 @@
       <c r="A36" s="9" t="n"/>
       <c r="B36" s="6" t="inlineStr">
         <is>
+          <t>10:00～12:15</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>未来を創る会</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>原発学習</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>会</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="n"/>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>13:30～15:30</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>くまもと生涯学習インストラクターの会まなぶ</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>独楽吟</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>会</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>11月23日（月）</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>10:00～11:30</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>パレアひばりの会</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>フリートーキング</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>イ</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="n"/>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>10:00～12:30</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>懐かしい盆踊りの会</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>懐かしい盆踊りのボランティア会の打合せ、練習</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>イ</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="n"/>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>18:30～20:30</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>マイカ</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>フォークダンス</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>イ</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="n"/>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
           <t>14:00～16:30</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>未来を創る会</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>原発学習</t>
-        </is>
-      </c>
-      <c r="E36" s="8" t="inlineStr">
-        <is>
-          <t>会</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>10月26日（月）</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>10:00～11:45</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>ヨガ健康クラブ</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>ヨガ入門</t>
-        </is>
-      </c>
-      <c r="E37" s="8" t="inlineStr">
-        <is>
-          <t>イ</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="10" t="n"/>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>12:30～15:30</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>一般社団法人観光ボランティアガイド　くまもとよかとこ案内人の会</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>韓国語学習</t>
-        </is>
-      </c>
-      <c r="E38" s="8" t="inlineStr">
-        <is>
-          <t>イ</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="10" t="n"/>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>18:30～20:30</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>マイカ</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>フォークダンス</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="inlineStr">
-        <is>
-          <t>イ</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="10" t="n"/>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>14:00～16:30</t>
-        </is>
-      </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t>ブレーメンの音楽隊</t>
         </is>
       </c>
-      <c r="D40" s="7" t="inlineStr">
+      <c r="D41" s="7" t="inlineStr">
         <is>
           <t>音楽を楽しむ</t>
-        </is>
-      </c>
-      <c r="E40" s="8" t="inlineStr">
-        <is>
-          <t>会</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="9" t="n"/>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>17:30～19:30</t>
-        </is>
-      </c>
-      <c r="C41" s="7" t="inlineStr">
-        <is>
-          <t>CDLE熊本</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>ＣＤＬＥ熊本　生成ＡＩハンズオン勉強会（第4回）</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -1445,7 +1453,7 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>10月27日（火）</t>
+          <t>11月24日（火）</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
@@ -1470,7 +1478,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="10" t="n"/>
+      <c r="A43" s="9" t="n"/>
       <c r="B43" s="6" t="inlineStr">
         <is>
           <t>12:30～17:30</t>
@@ -1493,25 +1501,25 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="n"/>
+      <c r="A44" s="9" t="n"/>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>10:00～12:00</t>
+          <t>18:30～20:30</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>太極拳を楽しもう会</t>
+          <t>マイカ</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>健康太極拳</t>
+          <t>フォークダンス</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>会</t>
+          <t>イ</t>
         </is>
       </c>
     </row>
@@ -1519,17 +1527,17 @@
       <c r="A45" s="9" t="n"/>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>15:00～18:00</t>
+          <t>10:00～12:00</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>傾聴の誠（真）</t>
+          <t>太極拳を楽しもう会</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>心の勉強会で幸せになろう</t>
+          <t>健康太極拳</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
@@ -1539,29 +1547,25 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>10月28日（水）</t>
-        </is>
-      </c>
+      <c r="A46" s="9" t="n"/>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>10:00～12:30</t>
+          <t>13:00～15:00</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>懐かしい盆踊りの会</t>
+          <t>NPO法人傾聴ネットキーステーション</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>懐かしい盆踊りのボランティア会の打ち合わせ・練習</t>
+          <t>27期傾聴ボランティア養成講座(4回目)</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>イ</t>
+          <t>会</t>
         </is>
       </c>
     </row>
@@ -1569,72 +1573,72 @@
       <c r="A47" s="10" t="n"/>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>14:00～16:30</t>
+          <t>19:30～20:30</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>NPO法人でんでん虫の会</t>
+          <t>笑顔のたまて箱</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>おしゃべり会</t>
+          <t>人形劇の練習及び打合せ</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>イ</t>
+          <t>会</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="9" t="n"/>
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>11月25日（水）</t>
+        </is>
+      </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>10:00～12:20</t>
+          <t>9:40～11:30</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>からだケア</t>
+          <t>KKA高齢者健康友の会</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>からだケア</t>
+          <t>みんな笑顔で楽しく健康体操</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>会</t>
+          <t>イ</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>10月29日（木）</t>
-        </is>
-      </c>
+      <c r="A49" s="9" t="n"/>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>18:30～20:30</t>
+          <t>9:20～11:50</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>一般社団法人アイ・オー・イー（IOE）</t>
+          <t>楽しい健康吹き矢</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>くまもとNPOカレッジ2026</t>
+          <t>吹矢を楽しむ</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>イ</t>
+          <t>会</t>
         </is>
       </c>
     </row>
@@ -1642,17 +1646,17 @@
       <c r="A50" s="10" t="n"/>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>10:00～12:00</t>
+          <t>14:00～16:30</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>特定非営利活動法人　教育支援プロジェクト・マスターズ熊本</t>
+          <t>NPO法人でんでん虫の会</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>トークの会</t>
+          <t>おしゃべり会</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
@@ -1662,25 +1666,29 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="10" t="n"/>
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>11月26日（木）</t>
+        </is>
+      </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>13:10～15:20</t>
+          <t>18:30～20:30</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>熊本「新老人の会」</t>
+          <t>一般社団法人アイ・オー・イー（IOE）</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>スポーツ吹矢</t>
+          <t>くまもとNPOカレッジ２０２６</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>会</t>
+          <t>イ</t>
         </is>
       </c>
     </row>
@@ -1688,54 +1696,54 @@
       <c r="A52" s="9" t="n"/>
       <c r="B52" s="6" t="inlineStr">
         <is>
+          <t>10:00～15:00</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>NPO法人成年後見安心サポートネット熊本</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>成年後見無料相談会</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>会</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="n"/>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
           <t>18:30～20:30</t>
         </is>
       </c>
-      <c r="C52" s="7" t="inlineStr">
+      <c r="C53" s="7" t="inlineStr">
         <is>
           <t>熊本フォークダンスクラブ</t>
         </is>
       </c>
-      <c r="D52" s="7" t="inlineStr">
+      <c r="D53" s="7" t="inlineStr">
         <is>
           <t>フォークダンス練習会</t>
         </is>
       </c>
-      <c r="E52" s="8" t="inlineStr">
-        <is>
-          <t>会</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>10月30日（金）</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>13:00～17:30</t>
-        </is>
-      </c>
-      <c r="C53" s="7" t="inlineStr">
-        <is>
-          <t>囲碁普及会</t>
-        </is>
-      </c>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>囲碁の研究と対局</t>
-        </is>
-      </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>イ</t>
+          <t>会</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="10" t="n"/>
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>11月27日（金）</t>
+        </is>
+      </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
           <t>9:30～12:30</t>
@@ -1753,7 +1761,7 @@
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>イ・会</t>
+          <t>イ</t>
         </is>
       </c>
     </row>
@@ -1761,31 +1769,27 @@
       <c r="A55" s="9" t="n"/>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>13:20～17:10</t>
+          <t>13:00～17:30</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>楽しい健康吹き矢</t>
+          <t>囲碁普及会</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>吹矢を楽しむ</t>
+          <t>囲碁の研究と対局</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>会</t>
+          <t>イ</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>10月31日（土）</t>
-        </is>
-      </c>
+      <c r="A56" s="9" t="n"/>
       <c r="B56" s="6" t="inlineStr">
         <is>
           <t>10:00～11:30</t>
@@ -1793,40 +1797,40 @@
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>パレアひばりの会</t>
+          <t>熊本健康マージャン協会</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>フリートーキング</t>
+          <t>マージャン協会の座談会の打合せ</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>イ</t>
+          <t>会</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="10" t="n"/>
+      <c r="A57" s="9" t="n"/>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>14:00～15:00</t>
+          <t>13:20～15:30</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>英会話サークルGreenGables</t>
+          <t>エンジョイズ</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>英会話サロン</t>
+          <t>童謡・唱歌・懐かしい流行歌を楽しむ会</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>イ</t>
+          <t>会</t>
         </is>
       </c>
     </row>
@@ -1834,17 +1838,17 @@
       <c r="A58" s="10" t="n"/>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>10:00～12:30</t>
+          <t>18:30～20:40</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>特定非営利活動法人 教育支援プロジェクトマスターズ熊本</t>
+          <t>登校拒否・不登校に学ぶフレンズネットワークくまもと</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>親と子の成長を応援　親子多肉寄せ植えとリメイク鉢セミナー</t>
+          <t>フレンズ親の会</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
@@ -1854,47 +1858,47 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="9" t="n"/>
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>11月28日（土）</t>
+        </is>
+      </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>14:00～17:00</t>
+          <t>10:00～12:00</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>熊本生と死を考える会</t>
+          <t>くまもとぱれっと</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>熊本生と死を考える会</t>
+          <t>しめなわリース作り＋おしゃべり会</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>会</t>
+          <t>イ</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>11月1日（日）</t>
-        </is>
-      </c>
+      <c r="A60" s="9" t="n"/>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>13:40～16:30</t>
+          <t>13:00～15:50</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>ラジオ英語の会</t>
+          <t>熊本さわやかハイヤ俱楽部</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>英語を楽しもう</t>
+          <t>熊本の郷土芸能「牛深ハイヤ踊り」の練習</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
@@ -1907,49 +1911,45 @@
       <c r="A61" s="9" t="n"/>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>14:00～16:30</t>
+          <t>17:00～19:00</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>ブレーメンの音楽隊</t>
+          <t>一般社団法人 日本版DBS・BCP支援協会</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>音楽を楽しむ</t>
+          <t>こども性暴力防止法　施行１ヶ月前説明会</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>会</t>
+          <t>イ</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>11月2日（月）</t>
-        </is>
-      </c>
+      <c r="A62" s="9" t="n"/>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>10:00～11:50</t>
+          <t>14:00～17:00</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>ヨガ健康クラブ</t>
+          <t>傾聴の誠（真）</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>ヨガ入門</t>
+          <t>心の勉強会でもっと幸せになろう</t>
         </is>
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>イ</t>
+          <t>会</t>
         </is>
       </c>
     </row>
@@ -1957,40 +1957,44 @@
       <c r="A63" s="10" t="n"/>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>12:00～15:00</t>
+          <t>18:00～20:30</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>フラ・オ・レアレア</t>
+          <t>傾聴の誠（真）</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>フラダンスレッスン</t>
+          <t>誠（真）のグループカウンセリング</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>イ</t>
+          <t>会</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="10" t="n"/>
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>11月29日（日）</t>
+        </is>
+      </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>18:30～20:30</t>
+          <t>10:00～16:00</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>マイカ</t>
+          <t>Studio:B</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>フォークダンス</t>
+          <t>宇宙船地球号 ミッション！</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
@@ -2003,45 +2007,49 @@
       <c r="A65" s="10" t="n"/>
       <c r="B65" s="6" t="inlineStr">
         <is>
+          <t>13:30～15:30</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>NPO法人傾聴ネットキーステーション</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>定例会・事例検討会</t>
+        </is>
+      </c>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>会</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>11月30日（月）</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
           <t>10:00～11:50</t>
         </is>
       </c>
-      <c r="C65" s="7" t="inlineStr">
-        <is>
-          <t>さわやかボランティアーズ４班</t>
-        </is>
-      </c>
-      <c r="D65" s="7" t="inlineStr">
-        <is>
-          <t>さわやかボランティアーズ４班打合せ</t>
-        </is>
-      </c>
-      <c r="E65" s="8" t="inlineStr">
-        <is>
-          <t>会</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="10" t="n"/>
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t>14:00～15:30</t>
-        </is>
-      </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>ピエロン教室</t>
+          <t>ヨガ健康クラブ</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>マジックの練習</t>
+          <t>ヨガ入門</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>会</t>
+          <t>イ</t>
         </is>
       </c>
     </row>
@@ -2049,95 +2057,95 @@
       <c r="A67" s="9" t="n"/>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>17:20～20:30</t>
+          <t>18:30～20:30</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>楽しい健康吹き矢</t>
+          <t>マイカ</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>吹矢を楽しむ</t>
+          <t>フォークダンス</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>会</t>
+          <t>イ</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>11月3日（火）</t>
-        </is>
-      </c>
+      <c r="A68" s="10" t="n"/>
       <c r="B68" s="6" t="inlineStr">
         <is>
+          <t>14:00～18:00</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>傾聴の誠（真）</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>心の勉強会でもっと幸せになろう</t>
+        </is>
+      </c>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>会</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>12月1日（火）</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>10:00～11:30</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>世界の民族舞踊ペガサス</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>世界各地の民族の踊りを楽しもう（フォークダンス）</t>
+        </is>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>イ</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="9" t="n"/>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
           <t>12:30～17:30</t>
         </is>
       </c>
-      <c r="C68" s="7" t="inlineStr">
+      <c r="C70" s="7" t="inlineStr">
         <is>
           <t>囲碁普及会</t>
         </is>
       </c>
-      <c r="D68" s="7" t="inlineStr">
+      <c r="D70" s="7" t="inlineStr">
         <is>
           <t>囲碁の対局・初心者の指導と研究</t>
         </is>
       </c>
-      <c r="E68" s="8" t="inlineStr">
-        <is>
-          <t>イ</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="10" t="n"/>
-      <c r="B69" s="6" t="inlineStr">
-        <is>
-          <t>18:30～20:30</t>
-        </is>
-      </c>
-      <c r="C69" s="7" t="inlineStr">
-        <is>
-          <t>マイカ</t>
-        </is>
-      </c>
-      <c r="D69" s="7" t="inlineStr">
-        <is>
-          <t>フォークダンス</t>
-        </is>
-      </c>
-      <c r="E69" s="8" t="inlineStr">
-        <is>
-          <t>イ</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="10" t="n"/>
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t>9:30～11:30</t>
-        </is>
-      </c>
-      <c r="C70" s="7" t="inlineStr">
-        <is>
-          <t>楽しいオリガミ</t>
-        </is>
-      </c>
-      <c r="D70" s="7" t="inlineStr">
-        <is>
-          <t>折紙製作勉強会</t>
-        </is>
-      </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>会</t>
+          <t>イ</t>
         </is>
       </c>
     </row>
@@ -2145,49 +2153,45 @@
       <c r="A71" s="9" t="n"/>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>13:00～15:00</t>
+          <t>18:30～20:30</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>NPO法人傾聴ネットキーステーション</t>
+          <t>マイカ</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>27期傾聴ボランティア養成講座(1回目)</t>
+          <t>フォークダンス</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>会</t>
+          <t>イ</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t>11月4日（水）</t>
-        </is>
-      </c>
+      <c r="A72" s="9" t="n"/>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>14:00～16:30</t>
+          <t>10:00～12:00</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>NPO法人でんでん虫の会</t>
+          <t>太極拳を楽しもう会</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>おしゃべり会</t>
+          <t>健康太極拳</t>
         </is>
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>イ</t>
+          <t>会</t>
         </is>
       </c>
     </row>
@@ -2195,17 +2199,17 @@
       <c r="A73" s="10" t="n"/>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>10:00～12:00</t>
+          <t>13:00～15:00</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>多胎サークル　ダブルハッピー</t>
+          <t>NPO法人傾聴ネットキーステーション</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>多胎サークル　ダブルハッピー</t>
+          <t>第27期傾聴ボランティア養成講座</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
@@ -2215,47 +2219,47 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="9" t="n"/>
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>12月2日（水）</t>
+        </is>
+      </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>13:10～15:50</t>
+          <t>9:30～12:00</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>楽画喜の会</t>
+          <t>楽しいオリガミ</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>絵画制作活動</t>
+          <t>折紙製作勉強会</t>
         </is>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>会</t>
+          <t>イ</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>11月5日（木）</t>
-        </is>
-      </c>
+      <c r="A75" s="9" t="n"/>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>12:30～14:30</t>
+          <t>14:00～16:30</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>懐かしい盆踊りの会</t>
+          <t>NPO法人でんでん虫の会</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>懐かしい盆踊りのボランティア会の打合せ、練習</t>
+          <t>おしゃべり会</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
@@ -2265,20 +2269,20 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="10" t="n"/>
+      <c r="A76" s="9" t="n"/>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>10:00～17:00</t>
+          <t>10:00～12:20</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>スマイリー健＆アロハ・スターハワイアンズ</t>
+          <t>からだケア</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>ウクレレを楽しもう♪</t>
+          <t>からだケア</t>
         </is>
       </c>
       <c r="E76" s="8" t="inlineStr">
@@ -2288,20 +2292,20 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="9" t="n"/>
+      <c r="A77" s="10" t="n"/>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>18:30～20:30</t>
+          <t>14:00～16:30</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>熊本フォークダンスクラブ</t>
+          <t>ブレーメンの音楽隊</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>フォークダンス練習会</t>
+          <t>音楽を楽しむ</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
@@ -2313,22 +2317,22 @@
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>11月6日（金）</t>
+          <t>12月3日（木）</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>9:30～12:30</t>
+          <t>10:00～12:00</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>シニアクラブうらら</t>
+          <t>懐かしい盆踊りの会</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>シニアいきいきサロン</t>
+          <t>懐かしい盆踊り会</t>
         </is>
       </c>
       <c r="E78" s="8" t="inlineStr">
@@ -2338,25 +2342,25 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="10" t="n"/>
+      <c r="A79" s="9" t="n"/>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>13:30～15:30</t>
+          <t>10:00～17:00</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>NPO法人熊本わくわく体操ボランティア協会</t>
+          <t>スマイリー健＆アロハ・スターハワイアンズ</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>いつでも・だれでも健康体操</t>
+          <t>ウクレレを楽しもう</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>イ</t>
+          <t>会</t>
         </is>
       </c>
     </row>
@@ -2364,17 +2368,17 @@
       <c r="A80" s="10" t="n"/>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>10:00～11:30</t>
+          <t>18:30～20:30</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>熊本健康マージャン協会</t>
+          <t>熊本フォークダンスクラブ</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>マージャン協会の座談会</t>
+          <t>フォークダンス練習会</t>
         </is>
       </c>
       <c r="E80" s="8" t="inlineStr">
@@ -2384,47 +2388,47 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="9" t="n"/>
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>12月4日（金）</t>
+        </is>
+      </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>14:30～17:30</t>
+          <t>9:30～12:30</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>スマイリー健＆アロハ・スターハワイアンズ</t>
+          <t>シニアクラブうらら</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>♪ハワイアン・懐メロ演奏会♪</t>
+          <t>シニアいきいきサロン</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>会</t>
+          <t>イ</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>11月7日（土）</t>
-        </is>
-      </c>
+      <c r="A82" s="9" t="n"/>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>13:30～16:30</t>
+          <t>13:30～15:30</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>東教養囲碁研究会</t>
+          <t>NPO法人　熊本わくわく体操ボランティア協会</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>囲碁による人間形成・修練</t>
+          <t>いつでも・だれでも健康体操</t>
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr">
@@ -2437,17 +2441,17 @@
       <c r="A83" s="10" t="n"/>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>10:00～13:00</t>
+          <t>14:30～17:30</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>特定非営利活動法人教育支援プロジェクトマスターズ熊本</t>
+          <t>スマイリー健＆アロハ・スターハワイアンズ</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>教育支援プロジェクトマスターズ熊本20周年記念事業</t>
+          <t>ハワイアン・懐メロ演奏会</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
@@ -2457,7 +2461,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="9" t="n"/>
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>12月5日（土）</t>
+        </is>
+      </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
           <t>13:30～16:30</t>
@@ -2465,62 +2473,58 @@
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>傾聴ボランティアくまもと</t>
+          <t>東教養囲碁研究会</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>傾聴定例会</t>
+          <t>囲碁による人間形成・修練</t>
         </is>
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>会</t>
+          <t>イ</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="5" t="inlineStr">
-        <is>
-          <t>11月8日（日）</t>
-        </is>
-      </c>
+      <c r="A85" s="9" t="n"/>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>10:00～12:00</t>
+          <t>10:00～11:10</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>さわやか南京玉すだれを楽しむ会</t>
+          <t>口からの健康づくり歯っぴーかむカム</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>南京玉すだれの練習</t>
+          <t>ベロタッチ生活養生・食養生</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>イ</t>
+          <t>会</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="9" t="n"/>
+      <c r="A86" s="10" t="n"/>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>10:00～11:10</t>
+          <t>13:10～15:50</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>口からの健康づくり 歯っぴーかむカム</t>
+          <t>楽画喜の会</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>ベロタッチ生活養生・食養生</t>
+          <t>絵画制作活動</t>
         </is>
       </c>
       <c r="E86" s="8" t="inlineStr">
@@ -2532,22 +2536,22 @@
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>11月9日（月）</t>
+          <t>12月6日（日）</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>18:30～20:30</t>
+          <t>10:00～12:00</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>マイカ</t>
+          <t>さわやか南京玉すだれを楽しむ会</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>フォークダンス</t>
+          <t>南京玉すだれの練習</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
@@ -2557,24 +2561,20 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="5" t="inlineStr">
-        <is>
-          <t>11月10日（火）</t>
-        </is>
-      </c>
+      <c r="A88" s="9" t="n"/>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>9:30～12:00</t>
+          <t>13:40～16:30</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>はなの風</t>
+          <t>ラジオ英語の会</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>はなの風（水彩画教室）</t>
+          <t>英語を楽しもう</t>
         </is>
       </c>
       <c r="E88" s="8" t="inlineStr">
@@ -2587,40 +2587,44 @@
       <c r="A89" s="10" t="n"/>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>12:30～17:30</t>
+          <t>14:00～20:30</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>囲碁普及会</t>
+          <t>傾聴の誠（真）</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>囲碁の対局・初心者の指導と研究</t>
+          <t>言葉と心の断捨離供養！！</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>イ</t>
+          <t>会</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="10" t="n"/>
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>12月7日（月）</t>
+        </is>
+      </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>19:00～20:30</t>
+          <t>12:00～15:00</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>熊本市キャンプ協会</t>
+          <t>フラオレアレア</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>定例会</t>
+          <t>フラダンスレッスン</t>
         </is>
       </c>
       <c r="E90" s="8" t="inlineStr">
@@ -2630,43 +2634,43 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="10" t="n"/>
+      <c r="A91" s="9" t="n"/>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>10:00～12:00</t>
+          <t>18:30～20:30</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>太極拳を楽しもう会</t>
+          <t>マイカ</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>健康太極拳</t>
+          <t>フォークダンス</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>会</t>
+          <t>イ</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="10" t="n"/>
+      <c r="A92" s="9" t="n"/>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>13:00～15:00</t>
+          <t>9:10～11:50</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>NPO法人傾聴ネットキーステーション</t>
+          <t>熊本県おかあさんコーラス連盟</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>27期傾聴ボランティア養成講座(2回目)</t>
+          <t>熊本県おかあさんコーラス連盟　第１２回運営委員会</t>
         </is>
       </c>
       <c r="E92" s="8" t="inlineStr">
@@ -2676,20 +2680,20 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="9" t="n"/>
+      <c r="A93" s="10" t="n"/>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>19:30～20:30</t>
+          <t>13:10～15:20</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>笑顔のたまて箱</t>
+          <t>熊本「新老人の会」</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>人形劇の練習及び打合せ</t>
+          <t>スポーツ吹矢</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
@@ -2701,22 +2705,22 @@
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>11月11日（水）</t>
+          <t>12月8日（火）</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>9:40～11:30</t>
+          <t>9:30～11:30</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>KKA高齢者健康友の会</t>
+          <t>世界の民族舞踊ペガサス</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>みんな笑顔で楽しく健康体操</t>
+          <t>世界各地の民族の踊りを楽しもう（フォークダンス）</t>
         </is>
       </c>
       <c r="E94" s="8" t="inlineStr">
@@ -2726,20 +2730,20 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="10" t="n"/>
+      <c r="A95" s="9" t="n"/>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>10:00～12:00</t>
+          <t>12:30～17:30</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>（一社）熊本県助産師会</t>
+          <t>囲碁普及会</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>ママ＆ベビー教室</t>
+          <t>囲碁の対局・初心者の指導と研究</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
@@ -2749,20 +2753,20 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="10" t="n"/>
+      <c r="A96" s="9" t="n"/>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>14:00～16:30</t>
+          <t>18:30～20:30</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>NPO法人でんでん虫の会</t>
+          <t>マイカ</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>おしゃべり会</t>
+          <t>フォークダンス</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
@@ -2775,17 +2779,17 @@
       <c r="A97" s="9" t="n"/>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>13:30～17:30</t>
+          <t>9:30～12:00</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>「アミーゴ」</t>
+          <t>はなの風</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>「アミーゴ」バンド活動</t>
+          <t>はなの風（水彩画教室）</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
@@ -2795,29 +2799,25 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="5" t="inlineStr">
-        <is>
-          <t>11月13日（金）</t>
-        </is>
-      </c>
+      <c r="A98" s="9" t="n"/>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>13:00～17:30</t>
+          <t>13:20～15:30</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>囲碁普及会</t>
+          <t>エンジョイズ</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>囲碁の研究と対局</t>
+          <t>童謡唱歌懐かしい流行歌を楽しむ会</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>イ</t>
+          <t>会</t>
         </is>
       </c>
     </row>
@@ -2825,68 +2825,72 @@
       <c r="A99" s="10" t="n"/>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>18:30～20:30</t>
+          <t>19:00～20:30</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>一般社団法人アイ・オー・イー（IOE）</t>
+          <t>熊本市キャンプ協会</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>くまもとNPOカレッジ2026</t>
+          <t>定例会</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>イ</t>
+          <t>会</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="10" t="n"/>
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>12月9日（水）</t>
+        </is>
+      </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>9:30～12:30</t>
+          <t>9:40～11:30</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>シニアクラブうらら</t>
+          <t>KKA高齢者健康友の会</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>シニアいきいきサロン</t>
+          <t>みんな笑顔で楽しい健康体操</t>
         </is>
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t>会</t>
+          <t>イ</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="10" t="n"/>
+      <c r="A101" s="9" t="n"/>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>12:30～17:00</t>
+          <t>14:00～16:30</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>AA九州・沖縄地域熊本地区</t>
+          <t>NPO法人でんでん虫の会</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>AA九州・沖縄地域 矯正・保護施設フォーラムin熊本</t>
+          <t>おしゃべり会</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>会</t>
+          <t>イ</t>
         </is>
       </c>
     </row>
@@ -2894,17 +2898,17 @@
       <c r="A102" s="9" t="n"/>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>18:30～20:30</t>
+          <t>10:00～12:00</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>熊本フォークダンスクラブ</t>
+          <t>（一社）熊本県助産師会</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>フォークダンス練習会</t>
+          <t>ママ＆ベビー教室</t>
         </is>
       </c>
       <c r="E102" s="8" t="inlineStr">
@@ -2914,47 +2918,47 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="5" t="inlineStr">
-        <is>
-          <t>11月14日（土）</t>
-        </is>
-      </c>
+      <c r="A103" s="10" t="n"/>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>9:00～11:50</t>
+          <t>13:30～17:30</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>熊本さわやかハイヤ俱楽部</t>
+          <t>「アミーゴ」</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>熊本の郷土芸能「牛深ハイヤ踊り」の練習</t>
+          <t>高齢者バンド</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>イ</t>
+          <t>会</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="10" t="n"/>
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>12月11日（金）</t>
+        </is>
+      </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>13:30～16:30</t>
+          <t>9:30～12:30</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>東教養囲碁研究会</t>
+          <t>シニアクラブうらら</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>囲碁による人間形成・修練</t>
+          <t>シニアいきいきサロン</t>
         </is>
       </c>
       <c r="E104" s="8" t="inlineStr">
@@ -2964,25 +2968,25 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="10" t="n"/>
+      <c r="A105" s="9" t="n"/>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>9:00～11:50</t>
+          <t>13:00～17:30</t>
         </is>
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>熊本史談会</t>
+          <t>囲碁普及会</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>熊本歴史の勉強会</t>
+          <t>囲碁の研究と対局</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>会</t>
+          <t>イ</t>
         </is>
       </c>
     </row>
@@ -2990,72 +2994,68 @@
       <c r="A106" s="9" t="n"/>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>13:30～16:30</t>
+          <t>18:30～20:30</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>登校拒否・不登校に学ぶフレンズネットワークくまもと</t>
+          <t>一般社団法人アイ・オー・イー（IOE）</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>フレンズ親の会</t>
+          <t>くまもとNPOカレッジ2026</t>
         </is>
       </c>
       <c r="E106" s="8" t="inlineStr">
         <is>
-          <t>会</t>
+          <t>イ</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="5" t="inlineStr">
-        <is>
-          <t>11月15日（日）</t>
-        </is>
-      </c>
+      <c r="A107" s="9" t="n"/>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>9:00～12:30</t>
+          <t>10:00～11:30</t>
         </is>
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>特定非営利活動法人 教育支援プロジェクトマスターズ熊本</t>
+          <t>熊本健康マージャン協会</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>親と子の体験　クリスマスプレート作り(陶磁器)</t>
+          <t>マージャン協会の座談会</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>イ</t>
+          <t>会</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="10" t="n"/>
+      <c r="A108" s="9" t="n"/>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>13:40～16:30</t>
+          <t>14:30～17:30</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>ラジオ英語の会</t>
+          <t>スマイリー健＆アロハ・スターハワイアンズ</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>英語を楽しもう</t>
+          <t>ハワイアン・懐メロ演奏会</t>
         </is>
       </c>
       <c r="E108" s="8" t="inlineStr">
         <is>
-          <t>イ</t>
+          <t>会</t>
         </is>
       </c>
     </row>
@@ -3063,17 +3063,17 @@
       <c r="A109" s="10" t="n"/>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>11:00～12:00</t>
+          <t>18:30～20:30</t>
         </is>
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>くまもと琵琶楽普及会</t>
+          <t>熊本フォークダンスクラブ</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>ワークショップ 琵琶の音色を楽しむ</t>
+          <t>フォークダンス練習会</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
@@ -3083,59 +3083,423 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="9" t="n"/>
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>12月12日（土）</t>
+        </is>
+      </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>15:00～17:30</t>
+          <t>9:30～11:50</t>
         </is>
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>「アミーゴ」</t>
+          <t>熊本さわやかハイヤ俱楽部</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>高齢者バンド</t>
+          <t>牛深ハイヤ踊りの練習</t>
         </is>
       </c>
       <c r="E110" s="8" t="inlineStr">
         <is>
+          <t>イ</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="9" t="n"/>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>13:30～16:30</t>
+        </is>
+      </c>
+      <c r="C111" s="7" t="inlineStr">
+        <is>
+          <t>東教養囲碁研究会</t>
+        </is>
+      </c>
+      <c r="D111" s="7" t="inlineStr">
+        <is>
+          <t>囲碁による人間形成・修練</t>
+        </is>
+      </c>
+      <c r="E111" s="8" t="inlineStr">
+        <is>
+          <t>イ</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="9" t="n"/>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>10:00～11:30</t>
+        </is>
+      </c>
+      <c r="C112" s="7" t="inlineStr">
+        <is>
+          <t>傾聴ボランティアくまもと</t>
+        </is>
+      </c>
+      <c r="D112" s="7" t="inlineStr">
+        <is>
+          <t>定例会</t>
+        </is>
+      </c>
+      <c r="E112" s="8" t="inlineStr">
+        <is>
+          <t>会</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="10" t="n"/>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>13:30～15:30</t>
+        </is>
+      </c>
+      <c r="C113" s="7" t="inlineStr">
+        <is>
+          <t>熊本県エスペラント会</t>
+        </is>
+      </c>
+      <c r="D113" s="7" t="inlineStr">
+        <is>
+          <t>ザメンホフ祭</t>
+        </is>
+      </c>
+      <c r="E113" s="8" t="inlineStr">
+        <is>
+          <t>会</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>12月13日（日）</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>10:00～12:00</t>
+        </is>
+      </c>
+      <c r="C114" s="7" t="inlineStr">
+        <is>
+          <t>多胎サークルダブルハッピー</t>
+        </is>
+      </c>
+      <c r="D114" s="7" t="inlineStr">
+        <is>
+          <t>多胎サークルダブルハッピー</t>
+        </is>
+      </c>
+      <c r="E114" s="8" t="inlineStr">
+        <is>
+          <t>会</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="10" t="n"/>
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t>14:00～16:30</t>
+        </is>
+      </c>
+      <c r="C115" s="7" t="inlineStr">
+        <is>
+          <t>ブレーメンの音楽隊</t>
+        </is>
+      </c>
+      <c r="D115" s="7" t="inlineStr">
+        <is>
+          <t>音楽を楽しむ</t>
+        </is>
+      </c>
+      <c r="E115" s="8" t="inlineStr">
+        <is>
+          <t>会</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>12月14日（月）</t>
+        </is>
+      </c>
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>10:00～11:45</t>
+        </is>
+      </c>
+      <c r="C116" s="7" t="inlineStr">
+        <is>
+          <t>ヨガ健康クラブ</t>
+        </is>
+      </c>
+      <c r="D116" s="7" t="inlineStr">
+        <is>
+          <t>ヨガ入門</t>
+        </is>
+      </c>
+      <c r="E116" s="8" t="inlineStr">
+        <is>
+          <t>イ</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="9" t="n"/>
+      <c r="B117" s="6" t="inlineStr">
+        <is>
+          <t>13:10～14:50</t>
+        </is>
+      </c>
+      <c r="C117" s="7" t="inlineStr">
+        <is>
+          <t>カフェてくてく会</t>
+        </is>
+      </c>
+      <c r="D117" s="7" t="inlineStr">
+        <is>
+          <t>カフェ　てくてく会</t>
+        </is>
+      </c>
+      <c r="E117" s="8" t="inlineStr">
+        <is>
+          <t>イ</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="9" t="n"/>
+      <c r="B118" s="6" t="inlineStr">
+        <is>
+          <t>18:30～20:30</t>
+        </is>
+      </c>
+      <c r="C118" s="7" t="inlineStr">
+        <is>
+          <t>マイカ</t>
+        </is>
+      </c>
+      <c r="D118" s="7" t="inlineStr">
+        <is>
+          <t>フォークダンス</t>
+        </is>
+      </c>
+      <c r="E118" s="8" t="inlineStr">
+        <is>
+          <t>イ</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="9" t="n"/>
+      <c r="B119" s="6" t="inlineStr">
+        <is>
+          <t>10:00～11:30</t>
+        </is>
+      </c>
+      <c r="C119" s="7" t="inlineStr">
+        <is>
+          <t>ピエロン教室</t>
+        </is>
+      </c>
+      <c r="D119" s="7" t="inlineStr">
+        <is>
+          <t>マジックの練習</t>
+        </is>
+      </c>
+      <c r="E119" s="8" t="inlineStr">
+        <is>
+          <t>会</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="9" t="n"/>
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>13:30～16:50</t>
+        </is>
+      </c>
+      <c r="C120" s="7" t="inlineStr">
+        <is>
+          <t>熊本市居住支援協議会</t>
+        </is>
+      </c>
+      <c r="D120" s="7" t="inlineStr">
+        <is>
+          <t>あんしん住替え相談会</t>
+        </is>
+      </c>
+      <c r="E120" s="8" t="inlineStr">
+        <is>
+          <t>会</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="10" t="n"/>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>17:30～19:30</t>
+        </is>
+      </c>
+      <c r="C121" s="7" t="inlineStr">
+        <is>
+          <t>CDLE熊本</t>
+        </is>
+      </c>
+      <c r="D121" s="7" t="inlineStr">
+        <is>
+          <t>ＣＤＬＥ熊本　生成ＡＩハンズオン勉強会（第6回）</t>
+        </is>
+      </c>
+      <c r="E121" s="8" t="inlineStr">
+        <is>
+          <t>会</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t>12月15日（火）</t>
+        </is>
+      </c>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>9:30～11:30</t>
+        </is>
+      </c>
+      <c r="C122" s="7" t="inlineStr">
+        <is>
+          <t>世界の民族舞踊ペガサス</t>
+        </is>
+      </c>
+      <c r="D122" s="7" t="inlineStr">
+        <is>
+          <t>世界各地の民族の踊りを楽しもう（フォークダンス）</t>
+        </is>
+      </c>
+      <c r="E122" s="8" t="inlineStr">
+        <is>
+          <t>イ</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="9" t="n"/>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>18:30～20:30</t>
+        </is>
+      </c>
+      <c r="C123" s="7" t="inlineStr">
+        <is>
+          <t>マイカ</t>
+        </is>
+      </c>
+      <c r="D123" s="7" t="inlineStr">
+        <is>
+          <t>フォークダンス</t>
+        </is>
+      </c>
+      <c r="E123" s="8" t="inlineStr">
+        <is>
+          <t>イ</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="9" t="n"/>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>10:00～12:00</t>
+        </is>
+      </c>
+      <c r="C124" s="7" t="inlineStr">
+        <is>
+          <t>太極拳を楽しもう会</t>
+        </is>
+      </c>
+      <c r="D124" s="7" t="inlineStr">
+        <is>
+          <t>健康太極拳</t>
+        </is>
+      </c>
+      <c r="E124" s="8" t="inlineStr">
+        <is>
+          <t>会</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="10" t="n"/>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>13:00～15:00</t>
+        </is>
+      </c>
+      <c r="C125" s="7" t="inlineStr">
+        <is>
+          <t>NPO法人傾聴ネットキーステーション</t>
+        </is>
+      </c>
+      <c r="D125" s="7" t="inlineStr">
+        <is>
+          <t>第27期傾聴ボランティア養成講座</t>
+        </is>
+      </c>
+      <c r="E125" s="8" t="inlineStr">
+        <is>
           <t>会</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="29">
-    <mergeCell ref="A94:A97"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="A107:A110"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A72:A74"/>
+  <mergeCells count="32">
+    <mergeCell ref="A110:A113"/>
+    <mergeCell ref="A5:A9"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A78:A81"/>
-    <mergeCell ref="A103:A106"/>
-    <mergeCell ref="A53:A55"/>
-    <mergeCell ref="A88:A93"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="A56:A59"/>
-    <mergeCell ref="A28:A32"/>
-    <mergeCell ref="A85:A86"/>
-    <mergeCell ref="A33:A36"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="A81:A83"/>
+    <mergeCell ref="A94:A99"/>
+    <mergeCell ref="A90:A93"/>
+    <mergeCell ref="A74:A77"/>
+    <mergeCell ref="A21:A24"/>
+    <mergeCell ref="A59:A63"/>
     <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A18:A23"/>
+    <mergeCell ref="A48:A50"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A82:A84"/>
-    <mergeCell ref="A42:A45"/>
-    <mergeCell ref="A98:A102"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A75:A77"/>
-    <mergeCell ref="A68:A71"/>
-    <mergeCell ref="A46:A48"/>
-    <mergeCell ref="A24:A27"/>
-    <mergeCell ref="A37:A41"/>
-    <mergeCell ref="A49:A52"/>
-    <mergeCell ref="A62:A67"/>
+    <mergeCell ref="A51:A53"/>
+    <mergeCell ref="A84:A86"/>
+    <mergeCell ref="A100:A103"/>
+    <mergeCell ref="A87:A89"/>
+    <mergeCell ref="A104:A109"/>
+    <mergeCell ref="A69:A73"/>
+    <mergeCell ref="A116:A121"/>
+    <mergeCell ref="A54:A58"/>
+    <mergeCell ref="A66:A68"/>
+    <mergeCell ref="A78:A80"/>
+    <mergeCell ref="A122:A125"/>
+    <mergeCell ref="A42:A47"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="A25:A29"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="A16:A20"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="A10:A15"/>
+    <mergeCell ref="A114:A115"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
